--- a/LAB5/24_test_case.xlsx
+++ b/LAB5/24_test_case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oggy2\OneDrive\Máy tính\LAB_AT_OOSD\LAB5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D8A014-D528-4DEB-A5D2-2878E56769FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C08502-3018-4EAC-BD1C-6425D5C47A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="99">
   <si>
     <t>BẢNG KIỂM THỬ 24 TEST CASE – QUẢN LÝ CÔNG TY DU LỊCH</t>
   </si>
@@ -298,9 +298,6 @@
     <t>Lương</t>
   </si>
   <si>
-    <t>Tháng 9/2026 (dữ liệu mẫu)</t>
-  </si>
-  <si>
     <t>HDV01: 10.500.000; HDV02: 11.500.000; HDV03: 10.500.000.</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
     <t>Thống kê</t>
   </si>
   <si>
-    <t>01/01/2026–01/10/2026</t>
-  </si>
-  <si>
     <t>Bảng 5 chỉ số; đăng ký lẻ 2 phiếu, 12.500.000 đ.</t>
   </si>
   <si>
@@ -332,6 +326,12 @@
   </si>
   <si>
     <t>Fail</t>
+  </si>
+  <si>
+    <t>01/01/2026–9/10/2026</t>
+  </si>
+  <si>
+    <t>Tháng 10/2026 (dữ liệu mẫu)</t>
   </si>
 </sst>
 </file>
@@ -446,6 +446,847 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>487077</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>304843</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A326BE55-BCA0-29B3-AA8C-248DAAFFC545}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="571500"/>
+          <a:ext cx="9326277" cy="304843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>458498</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>333422</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Hình ảnh 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0071844A-B56B-3A63-A5E0-50B7682FD7FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="1257300"/>
+          <a:ext cx="9297698" cy="333422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495837</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>222</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Hình ảnh 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21B35B5F-E864-DF21-BF94-317EF71C65BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="2028825"/>
+          <a:ext cx="3848637" cy="1590897"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>144214</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>666843</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Hình ảnh 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663A357E-868A-1379-3700-126C1719DE4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="3619500"/>
+          <a:ext cx="9593014" cy="666843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>29898</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>419158</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Hình ảnh 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9E399D9-0559-72A1-285C-9771AC4F6187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="4305300"/>
+          <a:ext cx="9478698" cy="419158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>343246</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1400370</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Hình ảnh 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A61CE39F-04AB-FAA6-C2CD-406C95F6EB03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="4991100"/>
+          <a:ext cx="2476846" cy="1400370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>553931</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1381318</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Hình ảnh 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0A6F77C-1CA3-E235-A49E-168E2047CD75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="7105650"/>
+          <a:ext cx="10612331" cy="1381318"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>305311</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1600423</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Hình ảnh 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30AA99B6-422A-1E01-FF87-0B99AD8C35AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="8582025"/>
+          <a:ext cx="3658111" cy="1600423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>553931</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Hình ảnh 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5069D084-855A-489E-A4C8-0C65FC339341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="10287000"/>
+          <a:ext cx="10612331" cy="1381318"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>410100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1743318</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Hình ảnh 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35BE0D8D-DA20-521B-F1FA-61625A484463}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="11658600"/>
+          <a:ext cx="3762900" cy="1743318"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>58477</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1143160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Hình ảnh 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C97CD0BF-5690-20D5-DCA1-5FF72B9F25F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="13458825"/>
+          <a:ext cx="9507277" cy="1143160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>296720</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1114581</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Hình ảnh 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A34EEF17-CFB4-0F89-51B0-30F6F5BFBC98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="14649450"/>
+          <a:ext cx="10355120" cy="1114581"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>476784</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66914</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Hình ảnh 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B416A22A-A9B6-4F2F-3928-FCAA533CEC3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="15944850"/>
+          <a:ext cx="3829584" cy="1714739"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1057275</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>277669</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66769</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Hình ảnh 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AC87C35-A865-45BC-ACF1-F1DE6253A198}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13058775" y="19145250"/>
+          <a:ext cx="10345594" cy="676369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>400404</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1428949</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Hình ảnh 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF5A7F2-5209-ACF8-334F-B8AFDDF69FDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="17592675"/>
+          <a:ext cx="2534004" cy="1428949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>458498</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>971686</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Hình ảnh 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C480788-B9D1-74A2-7E3A-71B096EFB57E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="21812250"/>
+          <a:ext cx="9297698" cy="971686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>29132</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1857634</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Hình ảnh 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A4E1D4-27A4-8DC2-B42B-625A715C685B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="23764875"/>
+          <a:ext cx="3991532" cy="1857634"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>106108</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3315163</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Hình ảnh 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36BC39FE-074C-CCEA-6A8F-CB743442F18F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="25641300"/>
+          <a:ext cx="9554908" cy="3315163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>458668</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>2734057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Hình ảnh 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B824676F-2CAE-F03B-E36D-CCA4BF1C88E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13068300" y="29079825"/>
+          <a:ext cx="10517068" cy="2734057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -792,9 +1633,11 @@
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -811,13 +1654,15 @@
       <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="132" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -830,9 +1675,11 @@
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -849,9 +1696,11 @@
       <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -868,13 +1717,15 @@
       <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -887,9 +1738,11 @@
       <c r="D8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -906,13 +1759,15 @@
       <c r="D9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -925,13 +1780,15 @@
       <c r="D10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -944,13 +1801,15 @@
       <c r="D11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -963,13 +1822,15 @@
       <c r="D12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>44</v>
       </c>
@@ -982,13 +1843,15 @@
       <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -1001,13 +1864,15 @@
       <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>51</v>
       </c>
@@ -1020,13 +1885,15 @@
       <c r="D15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>55</v>
       </c>
@@ -1039,13 +1906,15 @@
       <c r="D16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -1058,9 +1927,11 @@
       <c r="D17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -1077,9 +1948,11 @@
       <c r="D18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -1096,9 +1969,11 @@
       <c r="D19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F19" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -1115,9 +1990,11 @@
       <c r="D20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="F20" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G20" s="2"/>
     </row>
@@ -1134,13 +2011,15 @@
       <c r="D21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="F21" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>74</v>
       </c>
@@ -1153,9 +2032,11 @@
       <c r="D22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="F22" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22" s="2"/>
     </row>
@@ -1172,13 +2053,15 @@
       <c r="D23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F23" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>81</v>
       </c>
@@ -1191,13 +2074,15 @@
       <c r="D24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="F24" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="270.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -1205,33 +2090,37 @@
         <v>86</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="224.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3" t="s">
+      <c r="B26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="F26" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2"/>
     </row>
@@ -1246,6 +2135,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1260,21 +2150,21 @@
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTA('Kiem thu TC01-TC24'!A3:A26)</f>
@@ -1283,7 +2173,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Kiem thu TC01-TC24'!F3:F26,"Pass")</f>
@@ -1292,7 +2182,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Kiem thu TC01-TC24'!F3:F26,"Fail")</f>
